--- a/public/templates/shop-import-template.xlsx
+++ b/public/templates/shop-import-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ร้านค้า" sheetId="1" r:id="R5f1b4b5192c9492b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="วิธีกรอก" sheetId="2" r:id="Rc7d01157b73847eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ร้านค้า" sheetId="1" r:id="Rb48b3e85044546b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="วิธีกรอก" sheetId="2" r:id="Rceb1b95f8bcc456e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -663,7 +663,7 @@
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="23" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
@@ -726,7 +726,7 @@
         <x:v>รหัสร้าน</x:v>
       </x:c>
       <x:c r="G3" s="71" t="str">
-        <x:v>รหัสศูนย์ราชการ</x:v>
+        <x:v>รหัสล็อก/พื้นที่ขาย</x:v>
       </x:c>
       <x:c r="H3" s="71" t="str">
         <x:v>ชื่อร้าน</x:v>
@@ -13908,10 +13908,10 @@
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="92" t="str">
-        <x:v>รหัสศูนย์ราชการ</x:v>
+        <x:v>รหัสล็อก/พื้นที่ขาย</x:v>
       </x:c>
       <x:c r="B8" s="92" t="str">
-        <x:v>เว้นว่างได้ กรอกตามรหัสที่ศูนย์ราชการออกให้ ระบบไม่ใช้รหัสนี้แทนรหัสร้านภายใน</x:v>
+        <x:v>เว้นว่างได้ เป็นรหัสประจำพื้นที่ขายของศูนย์ราชการ ใช้ซ้ำได้เมื่อร้านเดิมพักใช้งาน แต่ห้ามมีร้านใช้งานพร้อมกันในล็อกเดียวกัน</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
@@ -13940,7 +13940,7 @@
     </x:row>
     <x:row r="13" ht="38" customHeight="1">
       <x:c r="A13" s="95" t="str">
-        <x:v>เมื่อนำเข้า รหัสที่มีอยู่แล้วจะถูกอัปเดตและทั้งไฟล์จะบันทึกพร้อมกัน หากตึกหรือโซนเดิมถูกพักใช้งาน ระบบจะหยุดและให้เปิดใช้งานจากหน้าตั้งค่าก่อน</x:v>
+        <x:v>เมื่อนำเข้า รหัสที่มีอยู่แล้วจะถูกอัปเดตและทั้งไฟล์จะบันทึกพร้อมกัน หากตึกหรือโซนเดิมถูกพักใช้งาน หรือมีร้านใช้งานใช้รหัสล็อกซ้ำ ระบบจะยกเลิกทั้งไฟล์</x:v>
       </x:c>
       <x:c r="B13" s="95"/>
       <x:c r="C13" s="95"/>
